--- a/docs/Frdm-k66f_pinout_mbed.xlsx
+++ b/docs/Frdm-k66f_pinout_mbed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jdaily\Documents\GitHub\SSS2\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A33E9966-0A27-4F64-8F9D-D9BC8C0B9A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4365E8D-9CAA-4209-BA95-271760ACD354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12" yWindow="-17388" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2364" yWindow="-14796" windowWidth="23040" windowHeight="12204" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FRDM_K66F Pin Mux" sheetId="4" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1676" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="777">
   <si>
     <t>A3</t>
   </si>
@@ -2353,6 +2353,9 @@
   </si>
   <si>
     <t>RedLEDPin</t>
+  </si>
+  <si>
+    <t>https://os.mbed.com/teams/NXP/wiki/FRDM-K66F-Pinnames</t>
   </si>
 </sst>
 </file>
@@ -2994,18 +2997,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -3018,10 +3009,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3444,10 +3447,10 @@
       </c>
     </row>
     <row r="2" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="67">
+      <c r="C2" s="63">
         <v>1</v>
       </c>
       <c r="D2" s="1"/>
@@ -3467,13 +3470,13 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="6"/>
-      <c r="S2" s="68" t="s">
+      <c r="S2" s="65" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="3" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="65"/>
-      <c r="C3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="64"/>
       <c r="D3" s="7"/>
       <c r="E3" s="8" t="s">
         <v>659</v>
@@ -3497,14 +3500,14 @@
       </c>
       <c r="Q3" s="10"/>
       <c r="R3" s="12"/>
-      <c r="S3" s="69"/>
+      <c r="S3" s="66"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B4" s="65"/>
-      <c r="C4" s="60">
+      <c r="B4" s="61"/>
+      <c r="C4" s="64">
         <v>2</v>
       </c>
-      <c r="D4" s="61" t="s">
+      <c r="D4" s="68" t="s">
         <v>158</v>
       </c>
       <c r="E4" s="13" t="s">
@@ -3523,14 +3526,14 @@
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="17"/>
-      <c r="S4" s="61" t="s">
+      <c r="S4" s="68" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="5" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="65"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="69"/>
       <c r="E5" s="18" t="s">
         <v>660</v>
       </c>
@@ -3561,11 +3564,11 @@
       </c>
       <c r="Q5" s="20"/>
       <c r="R5" s="22"/>
-      <c r="S5" s="62"/>
+      <c r="S5" s="69"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B6" s="65"/>
-      <c r="C6" s="60">
+      <c r="B6" s="61"/>
+      <c r="C6" s="64">
         <v>3</v>
       </c>
       <c r="D6" s="1"/>
@@ -3587,8 +3590,8 @@
       <c r="R6" s="6"/>
     </row>
     <row r="7" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="65"/>
-      <c r="C7" s="60"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="64"/>
       <c r="D7" s="7"/>
       <c r="E7" s="8" t="s">
         <v>662</v>
@@ -3618,11 +3621,11 @@
       <c r="R7" s="12"/>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B8" s="65"/>
-      <c r="C8" s="60">
+      <c r="B8" s="61"/>
+      <c r="C8" s="64">
         <v>4</v>
       </c>
-      <c r="D8" s="61" t="s">
+      <c r="D8" s="68" t="s">
         <v>1</v>
       </c>
       <c r="E8" s="23" t="s">
@@ -3643,9 +3646,9 @@
       <c r="R8" s="17"/>
     </row>
     <row r="9" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="65"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="62"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="69"/>
       <c r="E9" s="24" t="s">
         <v>663</v>
       </c>
@@ -3676,8 +3679,8 @@
       <c r="R9" s="22"/>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="65"/>
-      <c r="C10" s="60">
+      <c r="B10" s="61"/>
+      <c r="C10" s="64">
         <v>5</v>
       </c>
       <c r="D10" s="1"/>
@@ -3699,8 +3702,8 @@
       <c r="R10" s="6"/>
     </row>
     <row r="11" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="65"/>
-      <c r="C11" s="60"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="64"/>
       <c r="D11" s="7"/>
       <c r="E11" s="8" t="s">
         <v>665</v>
@@ -3734,11 +3737,11 @@
       <c r="R11" s="12"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B12" s="65"/>
-      <c r="C12" s="60">
+      <c r="B12" s="61"/>
+      <c r="C12" s="64">
         <v>6</v>
       </c>
-      <c r="D12" s="61" t="s">
+      <c r="D12" s="68" t="s">
         <v>120</v>
       </c>
       <c r="E12" s="25" t="s">
@@ -3759,9 +3762,9 @@
       <c r="R12" s="17"/>
     </row>
     <row r="13" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="65"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="62"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="69"/>
       <c r="E13" s="18" t="s">
         <v>668</v>
       </c>
@@ -3786,8 +3789,8 @@
       <c r="R13" s="22"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="65"/>
-      <c r="C14" s="60">
+      <c r="B14" s="61"/>
+      <c r="C14" s="64">
         <v>7</v>
       </c>
       <c r="D14" s="1"/>
@@ -3811,8 +3814,8 @@
       <c r="R14" s="6"/>
     </row>
     <row r="15" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="65"/>
-      <c r="C15" s="60"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="64"/>
       <c r="D15" s="7"/>
       <c r="E15" s="8" t="s">
         <v>670</v>
@@ -3842,11 +3845,11 @@
       <c r="R15" s="12"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B16" s="65"/>
-      <c r="C16" s="60">
+      <c r="B16" s="61"/>
+      <c r="C16" s="64">
         <v>8</v>
       </c>
-      <c r="D16" s="61" t="s">
+      <c r="D16" s="68" t="s">
         <v>55</v>
       </c>
       <c r="E16" s="23" t="s">
@@ -3867,9 +3870,9 @@
       <c r="R16" s="17"/>
     </row>
     <row r="17" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="65"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="62"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="69"/>
       <c r="E17" s="24" t="s">
         <v>672</v>
       </c>
@@ -3898,8 +3901,8 @@
       <c r="R17" s="22"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" s="65"/>
-      <c r="C18" s="60">
+      <c r="B18" s="61"/>
+      <c r="C18" s="64">
         <v>9</v>
       </c>
       <c r="D18" s="1"/>
@@ -3923,8 +3926,8 @@
       <c r="R18" s="6"/>
     </row>
     <row r="19" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="65"/>
-      <c r="C19" s="60"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="64"/>
       <c r="D19" s="7"/>
       <c r="E19" s="8" t="s">
         <v>675</v>
@@ -3954,11 +3957,11 @@
       <c r="R19" s="12"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B20" s="65"/>
-      <c r="C20" s="60">
+      <c r="B20" s="61"/>
+      <c r="C20" s="64">
         <v>10</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="D20" s="68" t="s">
         <v>56</v>
       </c>
       <c r="E20" s="25" t="s">
@@ -3981,9 +3984,9 @@
       <c r="R20" s="17"/>
     </row>
     <row r="21" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="65"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="62"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="69"/>
       <c r="E21" s="18" t="s">
         <v>677</v>
       </c>
@@ -4008,8 +4011,8 @@
       <c r="R21" s="22"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B22" s="65"/>
-      <c r="C22" s="60">
+      <c r="B22" s="61"/>
+      <c r="C22" s="64">
         <v>11</v>
       </c>
       <c r="D22" s="1"/>
@@ -4031,8 +4034,8 @@
       <c r="R22" s="6"/>
     </row>
     <row r="23" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="65"/>
-      <c r="C23" s="60"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="64"/>
       <c r="D23" s="7"/>
       <c r="E23" s="8" t="s">
         <v>678</v>
@@ -4060,11 +4063,11 @@
       <c r="R23" s="12"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B24" s="65"/>
-      <c r="C24" s="60">
+      <c r="B24" s="61"/>
+      <c r="C24" s="64">
         <v>12</v>
       </c>
-      <c r="D24" s="61" t="s">
+      <c r="D24" s="68" t="s">
         <v>57</v>
       </c>
       <c r="E24" s="23" t="s">
@@ -4085,9 +4088,9 @@
       <c r="R24" s="17"/>
     </row>
     <row r="25" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="65"/>
-      <c r="C25" s="60"/>
-      <c r="D25" s="62"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="69"/>
       <c r="E25" s="24" t="s">
         <v>679</v>
       </c>
@@ -4118,11 +4121,11 @@
       <c r="R25" s="22"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B26" s="65"/>
-      <c r="C26" s="60">
+      <c r="B26" s="61"/>
+      <c r="C26" s="64">
         <v>13</v>
       </c>
-      <c r="D26" s="68"/>
+      <c r="D26" s="65"/>
       <c r="E26" s="2" t="s">
         <v>157</v>
       </c>
@@ -4143,9 +4146,9 @@
       <c r="R26" s="6"/>
     </row>
     <row r="27" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="65"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="69"/>
+      <c r="B27" s="61"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="66"/>
       <c r="E27" s="8" t="s">
         <v>681</v>
       </c>
@@ -4172,11 +4175,11 @@
       <c r="R27" s="12"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B28" s="65"/>
-      <c r="C28" s="60">
+      <c r="B28" s="61"/>
+      <c r="C28" s="64">
         <v>14</v>
       </c>
-      <c r="D28" s="61" t="s">
+      <c r="D28" s="68" t="s">
         <v>77</v>
       </c>
       <c r="E28" s="26" t="s">
@@ -4197,9 +4200,9 @@
       <c r="R28" s="17"/>
     </row>
     <row r="29" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="65"/>
-      <c r="C29" s="60"/>
-      <c r="D29" s="62"/>
+      <c r="B29" s="61"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="69"/>
       <c r="E29" s="27" t="s">
         <v>682</v>
       </c>
@@ -4234,8 +4237,8 @@
       <c r="R29" s="22"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B30" s="65"/>
-      <c r="C30" s="60">
+      <c r="B30" s="61"/>
+      <c r="C30" s="64">
         <v>15</v>
       </c>
       <c r="D30" s="1"/>
@@ -4257,8 +4260,8 @@
       <c r="R30" s="6"/>
     </row>
     <row r="31" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="65"/>
-      <c r="C31" s="60"/>
+      <c r="B31" s="61"/>
+      <c r="C31" s="64"/>
       <c r="D31" s="7"/>
       <c r="E31" s="8" t="s">
         <v>686</v>
@@ -4286,11 +4289,11 @@
       <c r="R31" s="12"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B32" s="65"/>
-      <c r="C32" s="60">
+      <c r="B32" s="61"/>
+      <c r="C32" s="64">
         <v>16</v>
       </c>
-      <c r="D32" s="61" t="s">
+      <c r="D32" s="68" t="s">
         <v>3</v>
       </c>
       <c r="E32" s="23" t="s">
@@ -4311,9 +4314,9 @@
       <c r="R32" s="17"/>
     </row>
     <row r="33" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="66"/>
-      <c r="C33" s="63"/>
-      <c r="D33" s="62"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="67"/>
+      <c r="D33" s="69"/>
       <c r="E33" s="24" t="s">
         <v>687</v>
       </c>
@@ -4336,13 +4339,13 @@
       <c r="R33" s="22"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B34" s="64" t="s">
+      <c r="B34" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="C34" s="67">
+      <c r="C34" s="63">
         <v>1</v>
       </c>
-      <c r="D34" s="68"/>
+      <c r="D34" s="65"/>
       <c r="E34" s="2" t="s">
         <v>157</v>
       </c>
@@ -4363,9 +4366,9 @@
       <c r="R34" s="6"/>
     </row>
     <row r="35" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="65"/>
-      <c r="C35" s="60"/>
-      <c r="D35" s="69"/>
+      <c r="B35" s="61"/>
+      <c r="C35" s="64"/>
+      <c r="D35" s="66"/>
       <c r="E35" s="8" t="s">
         <v>688</v>
       </c>
@@ -4388,11 +4391,11 @@
       <c r="R35" s="12"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B36" s="65"/>
-      <c r="C36" s="60">
+      <c r="B36" s="61"/>
+      <c r="C36" s="64">
         <v>2</v>
       </c>
-      <c r="D36" s="61" t="s">
+      <c r="D36" s="68" t="s">
         <v>2</v>
       </c>
       <c r="E36" s="25" t="s">
@@ -4415,9 +4418,9 @@
       <c r="R36" s="17"/>
     </row>
     <row r="37" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="65"/>
-      <c r="C37" s="60"/>
-      <c r="D37" s="62"/>
+      <c r="B37" s="61"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="69"/>
       <c r="E37" s="18" t="s">
         <v>691</v>
       </c>
@@ -4446,11 +4449,11 @@
       <c r="R37" s="22"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B38" s="65"/>
-      <c r="C38" s="60">
+      <c r="B38" s="61"/>
+      <c r="C38" s="64">
         <v>3</v>
       </c>
-      <c r="D38" s="68"/>
+      <c r="D38" s="65"/>
       <c r="E38" s="2" t="s">
         <v>157</v>
       </c>
@@ -4471,9 +4474,9 @@
       <c r="R38" s="6"/>
     </row>
     <row r="39" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="65"/>
-      <c r="C39" s="60"/>
-      <c r="D39" s="69"/>
+      <c r="B39" s="61"/>
+      <c r="C39" s="64"/>
+      <c r="D39" s="66"/>
       <c r="E39" s="8" t="s">
         <v>693</v>
       </c>
@@ -4494,11 +4497,11 @@
       <c r="R39" s="12"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B40" s="65"/>
-      <c r="C40" s="60">
+      <c r="B40" s="61"/>
+      <c r="C40" s="64">
         <v>4</v>
       </c>
-      <c r="D40" s="61" t="s">
+      <c r="D40" s="68" t="s">
         <v>79</v>
       </c>
       <c r="E40" s="23" t="s">
@@ -4521,9 +4524,9 @@
       <c r="R40" s="17"/>
     </row>
     <row r="41" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="65"/>
-      <c r="C41" s="60"/>
-      <c r="D41" s="62"/>
+      <c r="B41" s="61"/>
+      <c r="C41" s="64"/>
+      <c r="D41" s="69"/>
       <c r="E41" s="24" t="s">
         <v>695</v>
       </c>
@@ -4552,11 +4555,11 @@
       <c r="R41" s="22"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B42" s="65"/>
-      <c r="C42" s="60">
+      <c r="B42" s="61"/>
+      <c r="C42" s="64">
         <v>5</v>
       </c>
-      <c r="D42" s="68"/>
+      <c r="D42" s="65"/>
       <c r="E42" s="2" t="s">
         <v>157</v>
       </c>
@@ -4577,9 +4580,9 @@
       <c r="R42" s="6"/>
     </row>
     <row r="43" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="65"/>
-      <c r="C43" s="60"/>
-      <c r="D43" s="69"/>
+      <c r="B43" s="61"/>
+      <c r="C43" s="64"/>
+      <c r="D43" s="66"/>
       <c r="E43" s="8" t="s">
         <v>697</v>
       </c>
@@ -4604,11 +4607,11 @@
       <c r="R43" s="12"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B44" s="65"/>
-      <c r="C44" s="60">
+      <c r="B44" s="61"/>
+      <c r="C44" s="64">
         <v>6</v>
       </c>
-      <c r="D44" s="61" t="s">
+      <c r="D44" s="68" t="s">
         <v>78</v>
       </c>
       <c r="E44" s="25" t="s">
@@ -4629,9 +4632,9 @@
       <c r="R44" s="17"/>
     </row>
     <row r="45" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="65"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="62"/>
+      <c r="B45" s="61"/>
+      <c r="C45" s="64"/>
+      <c r="D45" s="69"/>
       <c r="E45" s="18" t="s">
         <v>701</v>
       </c>
@@ -4660,11 +4663,11 @@
       <c r="R45" s="22"/>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B46" s="65"/>
-      <c r="C46" s="60">
+      <c r="B46" s="61"/>
+      <c r="C46" s="64">
         <v>7</v>
       </c>
-      <c r="D46" s="68"/>
+      <c r="D46" s="65"/>
       <c r="E46" s="2" t="s">
         <v>157</v>
       </c>
@@ -4683,9 +4686,9 @@
       <c r="R46" s="6"/>
     </row>
     <row r="47" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="65"/>
-      <c r="C47" s="60"/>
-      <c r="D47" s="69"/>
+      <c r="B47" s="61"/>
+      <c r="C47" s="64"/>
+      <c r="D47" s="66"/>
       <c r="E47" s="8" t="s">
         <v>703</v>
       </c>
@@ -4714,11 +4717,11 @@
       <c r="R47" s="12"/>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B48" s="65"/>
-      <c r="C48" s="60">
+      <c r="B48" s="61"/>
+      <c r="C48" s="64">
         <v>8</v>
       </c>
-      <c r="D48" s="61" t="s">
+      <c r="D48" s="68" t="s">
         <v>53</v>
       </c>
       <c r="E48" s="23" t="s">
@@ -4739,9 +4742,9 @@
       <c r="R48" s="17"/>
     </row>
     <row r="49" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="65"/>
-      <c r="C49" s="60"/>
-      <c r="D49" s="62"/>
+      <c r="B49" s="61"/>
+      <c r="C49" s="64"/>
+      <c r="D49" s="69"/>
       <c r="E49" s="24" t="s">
         <v>704</v>
       </c>
@@ -4772,11 +4775,11 @@
       <c r="R49" s="22"/>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B50" s="65"/>
-      <c r="C50" s="60">
+      <c r="B50" s="61"/>
+      <c r="C50" s="64">
         <v>9</v>
       </c>
-      <c r="D50" s="68"/>
+      <c r="D50" s="65"/>
       <c r="E50" s="2" t="s">
         <v>157</v>
       </c>
@@ -4795,9 +4798,9 @@
       <c r="R50" s="6"/>
     </row>
     <row r="51" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="65"/>
-      <c r="C51" s="60"/>
-      <c r="D51" s="69"/>
+      <c r="B51" s="61"/>
+      <c r="C51" s="64"/>
+      <c r="D51" s="66"/>
       <c r="E51" s="8" t="s">
         <v>706</v>
       </c>
@@ -4826,11 +4829,11 @@
       <c r="R51" s="12"/>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B52" s="65"/>
-      <c r="C52" s="60">
+      <c r="B52" s="61"/>
+      <c r="C52" s="64">
         <v>10</v>
       </c>
-      <c r="D52" s="61" t="s">
+      <c r="D52" s="68" t="s">
         <v>162</v>
       </c>
       <c r="E52" s="25" t="s">
@@ -4851,9 +4854,9 @@
       <c r="R52" s="17"/>
     </row>
     <row r="53" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="65"/>
-      <c r="C53" s="60"/>
-      <c r="D53" s="62"/>
+      <c r="B53" s="61"/>
+      <c r="C53" s="64"/>
+      <c r="D53" s="69"/>
       <c r="E53" s="18" t="s">
         <v>707</v>
       </c>
@@ -4882,11 +4885,11 @@
       <c r="R53" s="22"/>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B54" s="65"/>
-      <c r="C54" s="60">
+      <c r="B54" s="61"/>
+      <c r="C54" s="64">
         <v>11</v>
       </c>
-      <c r="D54" s="68"/>
+      <c r="D54" s="65"/>
       <c r="E54" s="2" t="s">
         <v>157</v>
       </c>
@@ -4905,9 +4908,9 @@
       <c r="R54" s="6"/>
     </row>
     <row r="55" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="65"/>
-      <c r="C55" s="60"/>
-      <c r="D55" s="69"/>
+      <c r="B55" s="61"/>
+      <c r="C55" s="64"/>
+      <c r="D55" s="66"/>
       <c r="E55" s="8" t="s">
         <v>708</v>
       </c>
@@ -4936,11 +4939,11 @@
       <c r="R55" s="12"/>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B56" s="65"/>
-      <c r="C56" s="60">
+      <c r="B56" s="61"/>
+      <c r="C56" s="64">
         <v>12</v>
       </c>
-      <c r="D56" s="61" t="s">
+      <c r="D56" s="68" t="s">
         <v>163</v>
       </c>
       <c r="E56" s="23" t="s">
@@ -4961,9 +4964,9 @@
       <c r="R56" s="17"/>
     </row>
     <row r="57" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="65"/>
-      <c r="C57" s="60"/>
-      <c r="D57" s="62"/>
+      <c r="B57" s="61"/>
+      <c r="C57" s="64"/>
+      <c r="D57" s="69"/>
       <c r="E57" s="24" t="s">
         <v>711</v>
       </c>
@@ -4992,11 +4995,11 @@
       <c r="R57" s="22"/>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B58" s="65"/>
-      <c r="C58" s="60">
+      <c r="B58" s="61"/>
+      <c r="C58" s="64">
         <v>13</v>
       </c>
-      <c r="D58" s="68"/>
+      <c r="D58" s="65"/>
       <c r="E58" s="2" t="s">
         <v>157</v>
       </c>
@@ -5015,9 +5018,9 @@
       <c r="R58" s="6"/>
     </row>
     <row r="59" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="65"/>
-      <c r="C59" s="60"/>
-      <c r="D59" s="69"/>
+      <c r="B59" s="61"/>
+      <c r="C59" s="64"/>
+      <c r="D59" s="66"/>
       <c r="E59" s="8" t="s">
         <v>712</v>
       </c>
@@ -5046,11 +5049,11 @@
       <c r="R59" s="12"/>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B60" s="65"/>
-      <c r="C60" s="60">
+      <c r="B60" s="61"/>
+      <c r="C60" s="64">
         <v>14</v>
       </c>
-      <c r="D60" s="61" t="s">
+      <c r="D60" s="68" t="s">
         <v>160</v>
       </c>
       <c r="E60" s="26" t="s">
@@ -5071,9 +5074,9 @@
       <c r="R60" s="17"/>
     </row>
     <row r="61" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="65"/>
-      <c r="C61" s="60"/>
-      <c r="D61" s="62"/>
+      <c r="B61" s="61"/>
+      <c r="C61" s="64"/>
+      <c r="D61" s="69"/>
       <c r="E61" s="27"/>
       <c r="F61" s="19"/>
       <c r="G61" s="19"/>
@@ -5090,11 +5093,11 @@
       <c r="R61" s="22"/>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B62" s="65"/>
-      <c r="C62" s="60">
+      <c r="B62" s="61"/>
+      <c r="C62" s="64">
         <v>15</v>
       </c>
-      <c r="D62" s="68"/>
+      <c r="D62" s="65"/>
       <c r="E62" s="2" t="s">
         <v>157</v>
       </c>
@@ -5113,9 +5116,9 @@
       <c r="R62" s="6"/>
     </row>
     <row r="63" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="65"/>
-      <c r="C63" s="60"/>
-      <c r="D63" s="69"/>
+      <c r="B63" s="61"/>
+      <c r="C63" s="64"/>
+      <c r="D63" s="66"/>
       <c r="E63" s="8" t="s">
         <v>713</v>
       </c>
@@ -5146,11 +5149,11 @@
       <c r="R63" s="12"/>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B64" s="65"/>
-      <c r="C64" s="60">
+      <c r="B64" s="61"/>
+      <c r="C64" s="64">
         <v>16</v>
       </c>
-      <c r="D64" s="61" t="s">
+      <c r="D64" s="68" t="s">
         <v>164</v>
       </c>
       <c r="E64" s="13" t="s">
@@ -5171,9 +5174,9 @@
       <c r="R64" s="17"/>
     </row>
     <row r="65" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="65"/>
-      <c r="C65" s="60"/>
-      <c r="D65" s="62"/>
+      <c r="B65" s="61"/>
+      <c r="C65" s="64"/>
+      <c r="D65" s="69"/>
       <c r="E65" s="18"/>
       <c r="F65" s="19"/>
       <c r="G65" s="19"/>
@@ -5190,8 +5193,8 @@
       <c r="R65" s="22"/>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B66" s="65"/>
-      <c r="C66" s="60">
+      <c r="B66" s="61"/>
+      <c r="C66" s="64">
         <v>17</v>
       </c>
       <c r="D66" s="1"/>
@@ -5213,8 +5216,8 @@
       <c r="R66" s="6"/>
     </row>
     <row r="67" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="65"/>
-      <c r="C67" s="60"/>
+      <c r="B67" s="61"/>
+      <c r="C67" s="64"/>
       <c r="D67" s="7"/>
       <c r="E67" s="8" t="s">
         <v>715</v>
@@ -5238,11 +5241,11 @@
       <c r="R67" s="12"/>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B68" s="65"/>
-      <c r="C68" s="60">
+      <c r="B68" s="61"/>
+      <c r="C68" s="64">
         <v>18</v>
       </c>
-      <c r="D68" s="61" t="s">
+      <c r="D68" s="68" t="s">
         <v>165</v>
       </c>
       <c r="E68" s="26" t="s">
@@ -5263,9 +5266,9 @@
       <c r="R68" s="17"/>
     </row>
     <row r="69" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="65"/>
-      <c r="C69" s="60"/>
-      <c r="D69" s="62"/>
+      <c r="B69" s="61"/>
+      <c r="C69" s="64"/>
+      <c r="D69" s="69"/>
       <c r="E69" s="18" t="s">
         <v>716</v>
       </c>
@@ -5296,11 +5299,11 @@
       <c r="R69" s="22"/>
     </row>
     <row r="70" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B70" s="65"/>
-      <c r="C70" s="60">
+      <c r="B70" s="61"/>
+      <c r="C70" s="64">
         <v>19</v>
       </c>
-      <c r="D70" s="68"/>
+      <c r="D70" s="65"/>
       <c r="E70" s="2" t="s">
         <v>157</v>
       </c>
@@ -5319,9 +5322,9 @@
       <c r="R70" s="6"/>
     </row>
     <row r="71" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="65"/>
-      <c r="C71" s="60"/>
-      <c r="D71" s="69"/>
+      <c r="B71" s="61"/>
+      <c r="C71" s="64"/>
+      <c r="D71" s="66"/>
       <c r="E71" s="8" t="s">
         <v>719</v>
       </c>
@@ -5346,11 +5349,11 @@
       <c r="R71" s="12"/>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B72" s="65"/>
-      <c r="C72" s="60">
+      <c r="B72" s="61"/>
+      <c r="C72" s="64">
         <v>20</v>
       </c>
-      <c r="D72" s="61" t="s">
+      <c r="D72" s="68" t="s">
         <v>166</v>
       </c>
       <c r="E72" s="13" t="s">
@@ -5371,9 +5374,9 @@
       <c r="R72" s="17"/>
     </row>
     <row r="73" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="66"/>
-      <c r="C73" s="63"/>
-      <c r="D73" s="62"/>
+      <c r="B73" s="62"/>
+      <c r="C73" s="67"/>
+      <c r="D73" s="69"/>
       <c r="E73" s="18" t="s">
         <v>718</v>
       </c>
@@ -5402,13 +5405,13 @@
       <c r="R73" s="22"/>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B74" s="64" t="s">
+      <c r="B74" s="60" t="s">
         <v>154</v>
       </c>
-      <c r="C74" s="67">
+      <c r="C74" s="63">
         <v>1</v>
       </c>
-      <c r="D74" s="68"/>
+      <c r="D74" s="65"/>
       <c r="E74" s="2" t="s">
         <v>157</v>
       </c>
@@ -5427,9 +5430,9 @@
       <c r="R74" s="6"/>
     </row>
     <row r="75" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="65"/>
-      <c r="C75" s="60"/>
-      <c r="D75" s="69"/>
+      <c r="B75" s="61"/>
+      <c r="C75" s="64"/>
+      <c r="D75" s="66"/>
       <c r="E75" s="8" t="s">
         <v>720</v>
       </c>
@@ -5452,11 +5455,11 @@
       </c>
     </row>
     <row r="76" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B76" s="65"/>
-      <c r="C76" s="60">
+      <c r="B76" s="61"/>
+      <c r="C76" s="64">
         <v>2</v>
       </c>
-      <c r="D76" s="61" t="s">
+      <c r="D76" s="68" t="s">
         <v>161</v>
       </c>
       <c r="E76" s="13"/>
@@ -5475,9 +5478,9 @@
       <c r="R76" s="39"/>
     </row>
     <row r="77" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="65"/>
-      <c r="C77" s="60"/>
-      <c r="D77" s="62"/>
+      <c r="B77" s="61"/>
+      <c r="C77" s="64"/>
+      <c r="D77" s="69"/>
       <c r="E77" s="18"/>
       <c r="F77" s="40"/>
       <c r="G77" s="40"/>
@@ -5494,11 +5497,11 @@
       <c r="R77" s="43"/>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B78" s="65"/>
-      <c r="C78" s="60">
+      <c r="B78" s="61"/>
+      <c r="C78" s="64">
         <v>3</v>
       </c>
-      <c r="D78" s="68"/>
+      <c r="D78" s="65"/>
       <c r="E78" s="2" t="s">
         <v>157</v>
       </c>
@@ -5517,9 +5520,9 @@
       <c r="R78" s="6"/>
     </row>
     <row r="79" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="65"/>
-      <c r="C79" s="60"/>
-      <c r="D79" s="69"/>
+      <c r="B79" s="61"/>
+      <c r="C79" s="64"/>
+      <c r="D79" s="66"/>
       <c r="E79" s="8" t="s">
         <v>722</v>
       </c>
@@ -5542,11 +5545,11 @@
       </c>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B80" s="65"/>
-      <c r="C80" s="60">
+      <c r="B80" s="61"/>
+      <c r="C80" s="64">
         <v>4</v>
       </c>
-      <c r="D80" s="61" t="s">
+      <c r="D80" s="68" t="s">
         <v>167</v>
       </c>
       <c r="E80" s="23" t="s">
@@ -5567,9 +5570,9 @@
       <c r="R80" s="39"/>
     </row>
     <row r="81" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="65"/>
-      <c r="C81" s="60"/>
-      <c r="D81" s="62"/>
+      <c r="B81" s="61"/>
+      <c r="C81" s="64"/>
+      <c r="D81" s="69"/>
       <c r="E81" s="24"/>
       <c r="F81" s="40"/>
       <c r="G81" s="40"/>
@@ -5586,11 +5589,11 @@
       <c r="R81" s="43"/>
     </row>
     <row r="82" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B82" s="65"/>
-      <c r="C82" s="60">
+      <c r="B82" s="61"/>
+      <c r="C82" s="64">
         <v>5</v>
       </c>
-      <c r="D82" s="68"/>
+      <c r="D82" s="65"/>
       <c r="E82" s="2" t="s">
         <v>157</v>
       </c>
@@ -5611,9 +5614,9 @@
       <c r="R82" s="6"/>
     </row>
     <row r="83" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="65"/>
-      <c r="C83" s="60"/>
-      <c r="D83" s="69"/>
+      <c r="B83" s="61"/>
+      <c r="C83" s="64"/>
+      <c r="D83" s="66"/>
       <c r="E83" s="8" t="s">
         <v>723</v>
       </c>
@@ -5640,11 +5643,11 @@
       <c r="R83" s="12"/>
     </row>
     <row r="84" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B84" s="65"/>
-      <c r="C84" s="60">
+      <c r="B84" s="61"/>
+      <c r="C84" s="64">
         <v>6</v>
       </c>
-      <c r="D84" s="61" t="s">
+      <c r="D84" s="68" t="s">
         <v>168</v>
       </c>
       <c r="E84" s="25" t="s">
@@ -5665,9 +5668,9 @@
       <c r="R84" s="39"/>
     </row>
     <row r="85" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="65"/>
-      <c r="C85" s="60"/>
-      <c r="D85" s="62"/>
+      <c r="B85" s="61"/>
+      <c r="C85" s="64"/>
+      <c r="D85" s="69"/>
       <c r="E85" s="18"/>
       <c r="F85" s="40"/>
       <c r="G85" s="40"/>
@@ -5684,11 +5687,11 @@
       <c r="R85" s="43"/>
     </row>
     <row r="86" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B86" s="65"/>
-      <c r="C86" s="60">
+      <c r="B86" s="61"/>
+      <c r="C86" s="64">
         <v>7</v>
       </c>
-      <c r="D86" s="68"/>
+      <c r="D86" s="65"/>
       <c r="E86" s="2" t="s">
         <v>157</v>
       </c>
@@ -5707,9 +5710,9 @@
       <c r="R86" s="6"/>
     </row>
     <row r="87" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="65"/>
-      <c r="C87" s="60"/>
-      <c r="D87" s="69"/>
+      <c r="B87" s="61"/>
+      <c r="C87" s="64"/>
+      <c r="D87" s="66"/>
       <c r="E87" s="8" t="s">
         <v>725</v>
       </c>
@@ -5732,11 +5735,11 @@
       <c r="R87" s="12"/>
     </row>
     <row r="88" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B88" s="65"/>
-      <c r="C88" s="60">
+      <c r="B88" s="61"/>
+      <c r="C88" s="64">
         <v>8</v>
       </c>
-      <c r="D88" s="61" t="s">
+      <c r="D88" s="68" t="s">
         <v>167</v>
       </c>
       <c r="E88" s="23" t="s">
@@ -5757,9 +5760,9 @@
       <c r="R88" s="39"/>
     </row>
     <row r="89" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B89" s="65"/>
-      <c r="C89" s="60"/>
-      <c r="D89" s="62"/>
+      <c r="B89" s="61"/>
+      <c r="C89" s="64"/>
+      <c r="D89" s="69"/>
       <c r="E89" s="24"/>
       <c r="F89" s="40"/>
       <c r="G89" s="40"/>
@@ -5776,11 +5779,11 @@
       <c r="R89" s="43"/>
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B90" s="65"/>
-      <c r="C90" s="60">
+      <c r="B90" s="61"/>
+      <c r="C90" s="64">
         <v>9</v>
       </c>
-      <c r="D90" s="68"/>
+      <c r="D90" s="65"/>
       <c r="E90" s="2" t="s">
         <v>157</v>
       </c>
@@ -5801,9 +5804,9 @@
       </c>
     </row>
     <row r="91" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B91" s="65"/>
-      <c r="C91" s="60"/>
-      <c r="D91" s="69"/>
+      <c r="B91" s="61"/>
+      <c r="C91" s="64"/>
+      <c r="D91" s="66"/>
       <c r="E91" s="8" t="s">
         <v>726</v>
       </c>
@@ -5830,11 +5833,11 @@
       </c>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B92" s="65"/>
-      <c r="C92" s="60">
+      <c r="B92" s="61"/>
+      <c r="C92" s="64">
         <v>10</v>
       </c>
-      <c r="D92" s="61" t="s">
+      <c r="D92" s="68" t="s">
         <v>169</v>
       </c>
       <c r="E92" s="25" t="s">
@@ -5855,9 +5858,9 @@
       <c r="R92" s="39"/>
     </row>
     <row r="93" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="65"/>
-      <c r="C93" s="60"/>
-      <c r="D93" s="62"/>
+      <c r="B93" s="61"/>
+      <c r="C93" s="64"/>
+      <c r="D93" s="69"/>
       <c r="E93" s="18"/>
       <c r="F93" s="40"/>
       <c r="G93" s="40"/>
@@ -5874,11 +5877,11 @@
       <c r="R93" s="43"/>
     </row>
     <row r="94" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B94" s="65"/>
-      <c r="C94" s="60">
+      <c r="B94" s="61"/>
+      <c r="C94" s="64">
         <v>11</v>
       </c>
-      <c r="D94" s="68"/>
+      <c r="D94" s="65"/>
       <c r="E94" s="2" t="s">
         <v>157</v>
       </c>
@@ -5901,9 +5904,9 @@
       </c>
     </row>
     <row r="95" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B95" s="65"/>
-      <c r="C95" s="60"/>
-      <c r="D95" s="69"/>
+      <c r="B95" s="61"/>
+      <c r="C95" s="64"/>
+      <c r="D95" s="66"/>
       <c r="E95" s="8" t="s">
         <v>729</v>
       </c>
@@ -5930,11 +5933,11 @@
       </c>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B96" s="65"/>
-      <c r="C96" s="60">
+      <c r="B96" s="61"/>
+      <c r="C96" s="64">
         <v>12</v>
       </c>
-      <c r="D96" s="61" t="s">
+      <c r="D96" s="68" t="s">
         <v>160</v>
       </c>
       <c r="E96" s="23" t="s">
@@ -5955,9 +5958,9 @@
       <c r="R96" s="39"/>
     </row>
     <row r="97" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="65"/>
-      <c r="C97" s="60"/>
-      <c r="D97" s="62"/>
+      <c r="B97" s="61"/>
+      <c r="C97" s="64"/>
+      <c r="D97" s="69"/>
       <c r="E97" s="24"/>
       <c r="F97" s="40"/>
       <c r="G97" s="40"/>
@@ -5974,11 +5977,11 @@
       <c r="R97" s="43"/>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B98" s="65"/>
-      <c r="C98" s="60">
+      <c r="B98" s="61"/>
+      <c r="C98" s="64">
         <v>13</v>
       </c>
-      <c r="D98" s="68"/>
+      <c r="D98" s="65"/>
       <c r="E98" s="2" t="s">
         <v>157</v>
       </c>
@@ -5999,9 +6002,9 @@
       <c r="R98" s="6"/>
     </row>
     <row r="99" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="65"/>
-      <c r="C99" s="60"/>
-      <c r="D99" s="69"/>
+      <c r="B99" s="61"/>
+      <c r="C99" s="64"/>
+      <c r="D99" s="66"/>
       <c r="E99" s="8" t="s">
         <v>733</v>
       </c>
@@ -6026,11 +6029,11 @@
       </c>
     </row>
     <row r="100" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B100" s="65"/>
-      <c r="C100" s="60">
+      <c r="B100" s="61"/>
+      <c r="C100" s="64">
         <v>14</v>
       </c>
-      <c r="D100" s="61" t="s">
+      <c r="D100" s="68" t="s">
         <v>160</v>
       </c>
       <c r="E100" s="26" t="s">
@@ -6051,9 +6054,9 @@
       <c r="R100" s="39"/>
     </row>
     <row r="101" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="65"/>
-      <c r="C101" s="60"/>
-      <c r="D101" s="62"/>
+      <c r="B101" s="61"/>
+      <c r="C101" s="64"/>
+      <c r="D101" s="69"/>
       <c r="E101" s="27"/>
       <c r="F101" s="40"/>
       <c r="G101" s="40"/>
@@ -6070,11 +6073,11 @@
       <c r="R101" s="43"/>
     </row>
     <row r="102" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B102" s="65"/>
-      <c r="C102" s="60">
+      <c r="B102" s="61"/>
+      <c r="C102" s="64">
         <v>15</v>
       </c>
-      <c r="D102" s="68"/>
+      <c r="D102" s="65"/>
       <c r="E102" s="2" t="s">
         <v>157</v>
       </c>
@@ -6095,9 +6098,9 @@
       <c r="R102" s="6"/>
     </row>
     <row r="103" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="65"/>
-      <c r="C103" s="60"/>
-      <c r="D103" s="69"/>
+      <c r="B103" s="61"/>
+      <c r="C103" s="64"/>
+      <c r="D103" s="66"/>
       <c r="E103" s="8" t="s">
         <v>735</v>
       </c>
@@ -6126,11 +6129,11 @@
       <c r="R103" s="12"/>
     </row>
     <row r="104" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B104" s="65"/>
-      <c r="C104" s="60">
+      <c r="B104" s="61"/>
+      <c r="C104" s="64">
         <v>16</v>
       </c>
-      <c r="D104" s="61" t="s">
+      <c r="D104" s="68" t="s">
         <v>170</v>
       </c>
       <c r="E104" s="23" t="s">
@@ -6151,9 +6154,9 @@
       <c r="R104" s="39"/>
     </row>
     <row r="105" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B105" s="66"/>
-      <c r="C105" s="63"/>
-      <c r="D105" s="62"/>
+      <c r="B105" s="62"/>
+      <c r="C105" s="67"/>
+      <c r="D105" s="69"/>
       <c r="E105" s="24"/>
       <c r="F105" s="40"/>
       <c r="G105" s="40"/>
@@ -6170,13 +6173,13 @@
       <c r="R105" s="43"/>
     </row>
     <row r="106" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B106" s="64" t="s">
+      <c r="B106" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="C106" s="67">
+      <c r="C106" s="63">
         <v>1</v>
       </c>
-      <c r="D106" s="68"/>
+      <c r="D106" s="65"/>
       <c r="E106" s="2" t="s">
         <v>157</v>
       </c>
@@ -6197,9 +6200,9 @@
       <c r="R106" s="6"/>
     </row>
     <row r="107" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B107" s="65"/>
-      <c r="C107" s="60"/>
-      <c r="D107" s="69"/>
+      <c r="B107" s="61"/>
+      <c r="C107" s="64"/>
+      <c r="D107" s="66"/>
       <c r="E107" s="44" t="s">
         <v>737</v>
       </c>
@@ -6220,11 +6223,11 @@
       <c r="R107" s="12"/>
     </row>
     <row r="108" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B108" s="65"/>
-      <c r="C108" s="60">
+      <c r="B108" s="61"/>
+      <c r="C108" s="64">
         <v>2</v>
       </c>
-      <c r="D108" s="61" t="s">
+      <c r="D108" s="68" t="s">
         <v>171</v>
       </c>
       <c r="E108" s="13" t="s">
@@ -6245,9 +6248,9 @@
       <c r="R108" s="17"/>
     </row>
     <row r="109" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="65"/>
-      <c r="C109" s="60"/>
-      <c r="D109" s="62"/>
+      <c r="B109" s="61"/>
+      <c r="C109" s="64"/>
+      <c r="D109" s="69"/>
       <c r="E109" s="18" t="s">
         <v>750</v>
       </c>
@@ -6270,11 +6273,11 @@
       <c r="R109" s="22"/>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B110" s="65"/>
-      <c r="C110" s="60">
+      <c r="B110" s="61"/>
+      <c r="C110" s="64">
         <v>3</v>
       </c>
-      <c r="D110" s="68"/>
+      <c r="D110" s="65"/>
       <c r="E110" s="2" t="s">
         <v>157</v>
       </c>
@@ -6295,9 +6298,9 @@
       <c r="R110" s="6"/>
     </row>
     <row r="111" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B111" s="65"/>
-      <c r="C111" s="60"/>
-      <c r="D111" s="69"/>
+      <c r="B111" s="61"/>
+      <c r="C111" s="64"/>
+      <c r="D111" s="66"/>
       <c r="E111" s="44" t="s">
         <v>739</v>
       </c>
@@ -6318,11 +6321,11 @@
       <c r="R111" s="12"/>
     </row>
     <row r="112" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B112" s="65"/>
-      <c r="C112" s="60">
+      <c r="B112" s="61"/>
+      <c r="C112" s="64">
         <v>4</v>
       </c>
-      <c r="D112" s="61" t="s">
+      <c r="D112" s="68" t="s">
         <v>104</v>
       </c>
       <c r="E112" s="13" t="s">
@@ -6343,9 +6346,9 @@
       <c r="R112" s="17"/>
     </row>
     <row r="113" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B113" s="65"/>
-      <c r="C113" s="60"/>
-      <c r="D113" s="62"/>
+      <c r="B113" s="61"/>
+      <c r="C113" s="64"/>
+      <c r="D113" s="69"/>
       <c r="E113" s="18" t="s">
         <v>751</v>
       </c>
@@ -6368,11 +6371,11 @@
       <c r="R113" s="22"/>
     </row>
     <row r="114" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B114" s="65"/>
-      <c r="C114" s="60">
+      <c r="B114" s="61"/>
+      <c r="C114" s="64">
         <v>5</v>
       </c>
-      <c r="D114" s="68"/>
+      <c r="D114" s="65"/>
       <c r="E114" s="2" t="s">
         <v>157</v>
       </c>
@@ -6393,9 +6396,9 @@
       <c r="R114" s="6"/>
     </row>
     <row r="115" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="65"/>
-      <c r="C115" s="60"/>
-      <c r="D115" s="69"/>
+      <c r="B115" s="61"/>
+      <c r="C115" s="64"/>
+      <c r="D115" s="66"/>
       <c r="E115" s="44" t="s">
         <v>740</v>
       </c>
@@ -6418,11 +6421,11 @@
       <c r="R115" s="12"/>
     </row>
     <row r="116" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B116" s="65"/>
-      <c r="C116" s="60">
+      <c r="B116" s="61"/>
+      <c r="C116" s="64">
         <v>6</v>
       </c>
-      <c r="D116" s="61" t="s">
+      <c r="D116" s="68" t="s">
         <v>103</v>
       </c>
       <c r="E116" s="13" t="s">
@@ -6443,9 +6446,9 @@
       <c r="R116" s="17"/>
     </row>
     <row r="117" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B117" s="65"/>
-      <c r="C117" s="60"/>
-      <c r="D117" s="62"/>
+      <c r="B117" s="61"/>
+      <c r="C117" s="64"/>
+      <c r="D117" s="69"/>
       <c r="E117" s="18" t="s">
         <v>752</v>
       </c>
@@ -6472,11 +6475,11 @@
       </c>
     </row>
     <row r="118" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B118" s="65"/>
-      <c r="C118" s="60">
+      <c r="B118" s="61"/>
+      <c r="C118" s="64">
         <v>7</v>
       </c>
-      <c r="D118" s="68"/>
+      <c r="D118" s="65"/>
       <c r="E118" s="2" t="s">
         <v>157</v>
       </c>
@@ -6497,9 +6500,9 @@
       <c r="R118" s="6"/>
     </row>
     <row r="119" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B119" s="65"/>
-      <c r="C119" s="60"/>
-      <c r="D119" s="69"/>
+      <c r="B119" s="61"/>
+      <c r="C119" s="64"/>
+      <c r="D119" s="66"/>
       <c r="E119" s="44" t="s">
         <v>743</v>
       </c>
@@ -6522,11 +6525,11 @@
       <c r="R119" s="12"/>
     </row>
     <row r="120" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B120" s="65"/>
-      <c r="C120" s="60">
+      <c r="B120" s="61"/>
+      <c r="C120" s="64">
         <v>8</v>
       </c>
-      <c r="D120" s="61" t="s">
+      <c r="D120" s="68" t="s">
         <v>0</v>
       </c>
       <c r="E120" s="13" t="s">
@@ -6547,9 +6550,9 @@
       <c r="R120" s="17"/>
     </row>
     <row r="121" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B121" s="65"/>
-      <c r="C121" s="60"/>
-      <c r="D121" s="62"/>
+      <c r="B121" s="61"/>
+      <c r="C121" s="64"/>
+      <c r="D121" s="69"/>
       <c r="E121" s="18" t="s">
         <v>753</v>
       </c>
@@ -6576,11 +6579,11 @@
       </c>
     </row>
     <row r="122" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B122" s="65"/>
-      <c r="C122" s="60">
+      <c r="B122" s="61"/>
+      <c r="C122" s="64">
         <v>9</v>
       </c>
-      <c r="D122" s="68"/>
+      <c r="D122" s="65"/>
       <c r="E122" s="2" t="s">
         <v>157</v>
       </c>
@@ -6601,9 +6604,9 @@
       <c r="R122" s="6"/>
     </row>
     <row r="123" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B123" s="65"/>
-      <c r="C123" s="60"/>
-      <c r="D123" s="69"/>
+      <c r="B123" s="61"/>
+      <c r="C123" s="64"/>
+      <c r="D123" s="66"/>
       <c r="E123" s="44" t="s">
         <v>749</v>
       </c>
@@ -6628,11 +6631,11 @@
       <c r="R123" s="12"/>
     </row>
     <row r="124" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B124" s="65"/>
-      <c r="C124" s="60">
+      <c r="B124" s="61"/>
+      <c r="C124" s="64">
         <v>10</v>
       </c>
-      <c r="D124" s="61" t="s">
+      <c r="D124" s="68" t="s">
         <v>102</v>
       </c>
       <c r="E124" s="13" t="s">
@@ -6653,9 +6656,9 @@
       <c r="R124" s="17"/>
     </row>
     <row r="125" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B125" s="65"/>
-      <c r="C125" s="60"/>
-      <c r="D125" s="62"/>
+      <c r="B125" s="61"/>
+      <c r="C125" s="64"/>
+      <c r="D125" s="69"/>
       <c r="E125" s="18" t="s">
         <v>754</v>
       </c>
@@ -6688,11 +6691,11 @@
       </c>
     </row>
     <row r="126" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B126" s="65"/>
-      <c r="C126" s="60">
+      <c r="B126" s="61"/>
+      <c r="C126" s="64">
         <v>11</v>
       </c>
-      <c r="D126" s="68"/>
+      <c r="D126" s="65"/>
       <c r="E126" s="2" t="s">
         <v>157</v>
       </c>
@@ -6711,9 +6714,9 @@
       <c r="R126" s="6"/>
     </row>
     <row r="127" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B127" s="65"/>
-      <c r="C127" s="60"/>
-      <c r="D127" s="69"/>
+      <c r="B127" s="61"/>
+      <c r="C127" s="64"/>
+      <c r="D127" s="66"/>
       <c r="E127" s="44" t="s">
         <v>748</v>
       </c>
@@ -6738,11 +6741,11 @@
       <c r="R127" s="12"/>
     </row>
     <row r="128" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B128" s="65"/>
-      <c r="C128" s="60">
+      <c r="B128" s="61"/>
+      <c r="C128" s="64">
         <v>12</v>
       </c>
-      <c r="D128" s="61" t="s">
+      <c r="D128" s="68" t="s">
         <v>94</v>
       </c>
       <c r="E128" s="13" t="s">
@@ -6763,9 +6766,9 @@
       <c r="R128" s="17"/>
     </row>
     <row r="129" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B129" s="66"/>
-      <c r="C129" s="63"/>
-      <c r="D129" s="62"/>
+      <c r="B129" s="62"/>
+      <c r="C129" s="67"/>
+      <c r="D129" s="69"/>
       <c r="E129" s="18" t="s">
         <v>758</v>
       </c>
@@ -6798,13 +6801,13 @@
       </c>
     </row>
     <row r="130" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B130" s="64" t="s">
+      <c r="B130" s="60" t="s">
         <v>657</v>
       </c>
-      <c r="C130" s="67">
+      <c r="C130" s="63">
         <v>1</v>
       </c>
-      <c r="D130" s="68" t="s">
+      <c r="D130" s="65" t="s">
         <v>160</v>
       </c>
       <c r="E130" s="2" t="s">
@@ -6825,9 +6828,9 @@
       <c r="R130" s="31"/>
     </row>
     <row r="131" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B131" s="65"/>
-      <c r="C131" s="60"/>
-      <c r="D131" s="69"/>
+      <c r="B131" s="61"/>
+      <c r="C131" s="64"/>
+      <c r="D131" s="66"/>
       <c r="E131" s="8" t="s">
         <v>160</v>
       </c>
@@ -6846,11 +6849,11 @@
       <c r="R131" s="35"/>
     </row>
     <row r="132" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B132" s="65"/>
-      <c r="C132" s="60">
+      <c r="B132" s="61"/>
+      <c r="C132" s="64">
         <v>2</v>
       </c>
-      <c r="D132" s="68" t="s">
+      <c r="D132" s="65" t="s">
         <v>167</v>
       </c>
       <c r="E132" s="2" t="s">
@@ -6871,9 +6874,9 @@
       <c r="R132" s="31"/>
     </row>
     <row r="133" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B133" s="65"/>
-      <c r="C133" s="60"/>
-      <c r="D133" s="69"/>
+      <c r="B133" s="61"/>
+      <c r="C133" s="64"/>
+      <c r="D133" s="66"/>
       <c r="E133" s="8" t="s">
         <v>167</v>
       </c>
@@ -6892,8 +6895,8 @@
       <c r="R133" s="35"/>
     </row>
     <row r="134" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B134" s="65"/>
-      <c r="C134" s="60">
+      <c r="B134" s="61"/>
+      <c r="C134" s="64">
         <v>3</v>
       </c>
       <c r="D134" s="1"/>
@@ -6915,8 +6918,8 @@
       <c r="R134" s="6"/>
     </row>
     <row r="135" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B135" s="65"/>
-      <c r="C135" s="60"/>
+      <c r="B135" s="61"/>
+      <c r="C135" s="64"/>
       <c r="D135" s="7"/>
       <c r="E135" s="44" t="s">
         <v>762</v>
@@ -6942,8 +6945,8 @@
       <c r="R135" s="12"/>
     </row>
     <row r="136" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B136" s="65"/>
-      <c r="C136" s="60">
+      <c r="B136" s="61"/>
+      <c r="C136" s="64">
         <v>4</v>
       </c>
       <c r="D136" s="1"/>
@@ -6967,8 +6970,8 @@
       <c r="R136" s="6"/>
     </row>
     <row r="137" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B137" s="65"/>
-      <c r="C137" s="60"/>
+      <c r="B137" s="61"/>
+      <c r="C137" s="64"/>
       <c r="D137" s="7"/>
       <c r="E137" s="44" t="s">
         <v>763</v>
@@ -6998,8 +7001,8 @@
       <c r="R137" s="12"/>
     </row>
     <row r="138" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B138" s="65"/>
-      <c r="C138" s="60">
+      <c r="B138" s="61"/>
+      <c r="C138" s="64">
         <v>5</v>
       </c>
       <c r="D138" s="1"/>
@@ -7023,8 +7026,8 @@
       <c r="R138" s="6"/>
     </row>
     <row r="139" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B139" s="65"/>
-      <c r="C139" s="60"/>
+      <c r="B139" s="61"/>
+      <c r="C139" s="64"/>
       <c r="D139" s="7"/>
       <c r="E139" s="44" t="s">
         <v>764</v>
@@ -7054,8 +7057,8 @@
       <c r="R139" s="12"/>
     </row>
     <row r="140" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B140" s="65"/>
-      <c r="C140" s="60">
+      <c r="B140" s="61"/>
+      <c r="C140" s="64">
         <v>6</v>
       </c>
       <c r="D140" s="1"/>
@@ -7081,8 +7084,8 @@
       <c r="R140" s="6"/>
     </row>
     <row r="141" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B141" s="65"/>
-      <c r="C141" s="60"/>
+      <c r="B141" s="61"/>
+      <c r="C141" s="64"/>
       <c r="D141" s="7"/>
       <c r="E141" s="44" t="s">
         <v>765</v>
@@ -7114,8 +7117,8 @@
       <c r="R141" s="12"/>
     </row>
     <row r="142" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B142" s="65"/>
-      <c r="C142" s="60">
+      <c r="B142" s="61"/>
+      <c r="C142" s="64">
         <v>7</v>
       </c>
       <c r="D142" s="1"/>
@@ -7139,8 +7142,8 @@
       <c r="R142" s="6"/>
     </row>
     <row r="143" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="65"/>
-      <c r="C143" s="60"/>
+      <c r="B143" s="61"/>
+      <c r="C143" s="64"/>
       <c r="D143" s="7"/>
       <c r="E143" s="44" t="s">
         <v>766</v>
@@ -7168,8 +7171,8 @@
       <c r="R143" s="12"/>
     </row>
     <row r="144" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B144" s="65"/>
-      <c r="C144" s="60">
+      <c r="B144" s="61"/>
+      <c r="C144" s="64">
         <v>8</v>
       </c>
       <c r="D144" s="1"/>
@@ -7191,8 +7194,8 @@
       <c r="R144" s="6"/>
     </row>
     <row r="145" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B145" s="66"/>
-      <c r="C145" s="63"/>
+      <c r="B145" s="62"/>
+      <c r="C145" s="67"/>
       <c r="D145" s="7"/>
       <c r="E145" s="44" t="s">
         <v>768</v>
@@ -7218,13 +7221,13 @@
       </c>
     </row>
     <row r="146" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B146" s="64" t="s">
+      <c r="B146" s="60" t="s">
         <v>658</v>
       </c>
-      <c r="C146" s="67">
+      <c r="C146" s="63">
         <v>1</v>
       </c>
-      <c r="D146" s="68" t="s">
+      <c r="D146" s="65" t="s">
         <v>167</v>
       </c>
       <c r="E146" s="2" t="s">
@@ -7245,9 +7248,9 @@
       <c r="R146" s="31"/>
     </row>
     <row r="147" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="65"/>
-      <c r="C147" s="60"/>
-      <c r="D147" s="69"/>
+      <c r="B147" s="61"/>
+      <c r="C147" s="64"/>
+      <c r="D147" s="66"/>
       <c r="E147" s="8" t="s">
         <v>167</v>
       </c>
@@ -7266,11 +7269,11 @@
       <c r="R147" s="35"/>
     </row>
     <row r="148" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B148" s="65"/>
-      <c r="C148" s="60">
+      <c r="B148" s="61"/>
+      <c r="C148" s="64">
         <v>2</v>
       </c>
-      <c r="D148" s="68" t="s">
+      <c r="D148" s="65" t="s">
         <v>160</v>
       </c>
       <c r="E148" s="2" t="s">
@@ -7291,9 +7294,9 @@
       <c r="R148" s="31"/>
     </row>
     <row r="149" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B149" s="65"/>
-      <c r="C149" s="60"/>
-      <c r="D149" s="69"/>
+      <c r="B149" s="61"/>
+      <c r="C149" s="64"/>
+      <c r="D149" s="66"/>
       <c r="E149" s="8" t="s">
         <v>160</v>
       </c>
@@ -7312,8 +7315,8 @@
       <c r="R149" s="35"/>
     </row>
     <row r="150" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B150" s="65"/>
-      <c r="C150" s="60">
+      <c r="B150" s="61"/>
+      <c r="C150" s="64">
         <v>3</v>
       </c>
       <c r="D150" s="1"/>
@@ -7335,8 +7338,8 @@
       <c r="R150" s="6"/>
     </row>
     <row r="151" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B151" s="65"/>
-      <c r="C151" s="60"/>
+      <c r="B151" s="61"/>
+      <c r="C151" s="64"/>
       <c r="D151" s="7"/>
       <c r="E151" s="44" t="s">
         <v>769</v>
@@ -7360,8 +7363,8 @@
       <c r="R151" s="12"/>
     </row>
     <row r="152" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B152" s="65"/>
-      <c r="C152" s="60">
+      <c r="B152" s="61"/>
+      <c r="C152" s="64">
         <v>4</v>
       </c>
       <c r="D152" s="1"/>
@@ -7383,8 +7386,8 @@
       <c r="R152" s="6"/>
     </row>
     <row r="153" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="66"/>
-      <c r="C153" s="63"/>
+      <c r="B153" s="62"/>
+      <c r="C153" s="67"/>
       <c r="D153" s="7"/>
       <c r="E153" s="44" t="s">
         <v>770</v>
@@ -7410,41 +7413,81 @@
   </sheetData>
   <autoFilter ref="D1:Q153" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="144">
-    <mergeCell ref="B146:B153"/>
-    <mergeCell ref="C146:C147"/>
-    <mergeCell ref="D146:D147"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="D148:D149"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="D126:D127"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:D119"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="D120:D121"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="D122:D123"/>
-    <mergeCell ref="B106:B129"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="D98:D99"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="B130:B145"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="D132:D133"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="B34:B73"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="B2:B33"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
     <mergeCell ref="S2:S3"/>
     <mergeCell ref="S4:S5"/>
     <mergeCell ref="D34:D35"/>
@@ -7469,6 +7512,20 @@
     <mergeCell ref="C110:C111"/>
     <mergeCell ref="C96:C97"/>
     <mergeCell ref="D96:D97"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="D98:D99"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="B130:B145"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="D132:D133"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="C144:C145"/>
     <mergeCell ref="D100:D101"/>
     <mergeCell ref="B74:B105"/>
     <mergeCell ref="C74:C75"/>
@@ -7479,81 +7536,27 @@
     <mergeCell ref="D78:D79"/>
     <mergeCell ref="C80:C81"/>
     <mergeCell ref="D80:D81"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="B34:B73"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="B2:B33"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B146:B153"/>
+    <mergeCell ref="C146:C147"/>
+    <mergeCell ref="D146:D147"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="D148:D149"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="D126:D127"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:D119"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="D122:D123"/>
+    <mergeCell ref="B106:B129"/>
   </mergeCells>
   <conditionalFormatting sqref="S25">
     <cfRule type="expression" dxfId="1" priority="2">
@@ -7710,7 +7713,9 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
+      <c r="B4" s="54" t="s">
+        <v>776</v>
+      </c>
       <c r="C4" s="54"/>
       <c r="D4" s="53" t="s">
         <v>201</v>
@@ -11390,7 +11395,9 @@
       <c r="A132" s="53" t="s">
         <v>548</v>
       </c>
-      <c r="B132" s="53"/>
+      <c r="B132" s="53" t="s">
+        <v>158</v>
+      </c>
       <c r="C132" s="53"/>
       <c r="D132" s="53" t="s">
         <v>34</v>
@@ -11472,7 +11479,9 @@
       <c r="A135" s="53" t="s">
         <v>552</v>
       </c>
-      <c r="B135" s="53"/>
+      <c r="B135" s="53" t="s">
+        <v>1</v>
+      </c>
       <c r="C135" s="53"/>
       <c r="D135" s="53" t="s">
         <v>36</v>
